--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T05:10:08+00:00</t>
+    <t>2026-09-03T05:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5876" uniqueCount="780">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5876" uniqueCount="781">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T05:17:43+00:00</t>
+    <t>2026-09-03T05:48:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1688,7 +1688,7 @@
     <t>valueCodeableConcept</t>
   </si>
   <si>
-    <t>Actual result</t>
+    <t>Nachweis oder Ausschluss des im Code benannten Ziels. Ein grenzwertiger Befund wird als 'Weakly positive' oder 'Equivocal result' berichtet — das ist eine Aussage und gehört deshalb hierher. Ein unbestimmbares Ergebnis, bei dem die Untersuchung gar keine verwertbare Aussage liefert (z. B. inhibierte PCR), wird dagegen über dataAbsentReason abgebildet.</t>
   </si>
   <si>
     <t>The information determined as a result of making the observation, if the information has a simple value.</t>
@@ -1771,6 +1771,9 @@
   <si>
     <t xml:space="preserve">Quantity
 </t>
+  </si>
+  <si>
+    <t>Actual result</t>
   </si>
   <si>
     <t>Observation.value[x]:valueQuantity.id</t>
@@ -14626,7 +14629,7 @@
         <v>557</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>530</v>
+        <v>558</v>
       </c>
       <c r="M116" t="s" s="2">
         <v>531</v>
@@ -14701,7 +14704,7 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>534</v>
@@ -14801,7 +14804,7 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>536</v>
@@ -14903,13 +14906,13 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>536</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>104</v>
@@ -14931,16 +14934,16 @@
         <v>77</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -15007,10 +15010,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15033,19 +15036,19 @@
         <v>85</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>77</v>
@@ -15094,7 +15097,7 @@
         <v>77</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>75</v>
@@ -15111,10 +15114,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15211,10 +15214,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -15313,13 +15316,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="B123" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="B123" t="s" s="2">
-        <v>577</v>
-      </c>
       <c r="C123" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>104</v>
@@ -15341,16 +15344,16 @@
         <v>77</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -15417,10 +15420,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15443,13 +15446,13 @@
         <v>77</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -15500,7 +15503,7 @@
         <v>77</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>75</v>
@@ -15517,10 +15520,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15546,22 +15549,22 @@
         <v>160</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N125" t="s" s="2">
         <v>328</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q125" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="R125" t="s" s="2">
         <v>77</v>
@@ -15585,10 +15588,10 @@
         <v>226</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>77</v>
@@ -15606,7 +15609,7 @@
         <v>77</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>75</v>
@@ -15623,10 +15626,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15652,16 +15655,16 @@
         <v>99</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N126" t="s" s="2">
         <v>328</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>77</v>
@@ -15710,7 +15713,7 @@
         <v>77</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>75</v>
@@ -15727,10 +15730,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15756,23 +15759,23 @@
         <v>126</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q127" s="2"/>
       <c r="R127" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="S127" t="s" s="2">
         <v>77</v>
@@ -15814,7 +15817,7 @@
         <v>77</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>75</v>
@@ -15823,7 +15826,7 @@
         <v>84</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>92</v>
@@ -15831,10 +15834,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15860,16 +15863,16 @@
         <v>160</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>77</v>
@@ -15918,7 +15921,7 @@
         <v>77</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>75</v>
@@ -15935,13 +15938,13 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>520</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D129" t="s" s="2">
         <v>77</v>
@@ -15963,10 +15966,10 @@
         <v>85</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>530</v>
+        <v>558</v>
       </c>
       <c r="M129" t="s" s="2">
         <v>531</v>
@@ -16041,13 +16044,13 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>520</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D130" t="s" s="2">
         <v>77</v>
@@ -16069,10 +16072,10 @@
         <v>85</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>530</v>
+        <v>558</v>
       </c>
       <c r="M130" t="s" s="2">
         <v>531</v>
@@ -16147,10 +16150,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -16176,16 +16179,16 @@
         <v>283</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>77</v>
@@ -16214,7 +16217,7 @@
       </c>
       <c r="Y131" s="2"/>
       <c r="Z131" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>77</v>
@@ -16232,7 +16235,7 @@
         <v>77</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>75</v>
@@ -16241,7 +16244,7 @@
         <v>84</v>
       </c>
       <c r="AI131" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AJ131" t="s" s="2">
         <v>92</v>
@@ -16249,14 +16252,14 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
@@ -16278,16 +16281,16 @@
         <v>283</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>77</v>
@@ -16315,10 +16318,10 @@
         <v>142</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>77</v>
@@ -16336,7 +16339,7 @@
         <v>77</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>75</v>
@@ -16353,10 +16356,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -16379,19 +16382,19 @@
         <v>77</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>77</v>
@@ -16440,7 +16443,7 @@
         <v>77</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>75</v>
@@ -16457,10 +16460,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -16486,13 +16489,13 @@
         <v>283</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -16521,10 +16524,10 @@
         <v>150</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>77</v>
@@ -16542,7 +16545,7 @@
         <v>77</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>75</v>
@@ -16559,10 +16562,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -16588,16 +16591,16 @@
         <v>283</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>77</v>
@@ -16626,7 +16629,7 @@
       </c>
       <c r="Y135" s="2"/>
       <c r="Z135" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>77</v>
@@ -16644,7 +16647,7 @@
         <v>77</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>75</v>
@@ -16661,10 +16664,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -16761,10 +16764,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -16863,10 +16866,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -16967,10 +16970,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -17067,10 +17070,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -17169,10 +17172,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -17273,10 +17276,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -17375,10 +17378,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -17479,10 +17482,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -17583,10 +17586,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -17687,10 +17690,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -17791,10 +17794,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -17817,16 +17820,16 @@
         <v>77</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -17876,7 +17879,7 @@
         <v>77</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>75</v>
@@ -17893,10 +17896,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -17993,10 +17996,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -18095,10 +18098,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -18197,10 +18200,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -18299,10 +18302,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -18401,10 +18404,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -18503,10 +18506,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -18529,16 +18532,16 @@
         <v>77</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -18588,7 +18591,7 @@
         <v>77</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>75</v>
@@ -18605,10 +18608,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -18705,10 +18708,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -18807,10 +18810,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -18909,10 +18912,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -19011,10 +19014,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -19113,10 +19116,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -19215,10 +19218,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -19241,19 +19244,19 @@
         <v>77</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>77</v>
@@ -19302,7 +19305,7 @@
         <v>77</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>75</v>
@@ -19314,15 +19317,15 @@
         <v>91</v>
       </c>
       <c r="AJ161" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -19419,10 +19422,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -19521,14 +19524,14 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="E164" s="2"/>
       <c r="F164" t="s" s="2">
@@ -19550,10 +19553,10 @@
         <v>105</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="N164" t="s" s="2">
         <v>108</v>
@@ -19608,7 +19611,7 @@
         <v>77</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>75</v>
@@ -19625,10 +19628,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -19651,16 +19654,16 @@
         <v>77</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -19710,7 +19713,7 @@
         <v>77</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>75</v>
@@ -19719,18 +19722,18 @@
         <v>84</v>
       </c>
       <c r="AI165" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AJ165" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -19753,16 +19756,16 @@
         <v>77</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -19812,27 +19815,27 @@
         <v>77</v>
       </c>
       <c r="AF166" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="AG166" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI166" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="AJ166" t="s" s="2">
         <v>712</v>
-      </c>
-      <c r="AG166" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH166" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI166" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="AJ166" t="s" s="2">
-        <v>711</v>
       </c>
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -19858,16 +19861,16 @@
         <v>283</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>77</v>
@@ -19895,10 +19898,10 @@
         <v>164</v>
       </c>
       <c r="Y167" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="Z167" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>77</v>
@@ -19916,7 +19919,7 @@
         <v>77</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>75</v>
@@ -19933,10 +19936,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -19962,16 +19965,16 @@
         <v>283</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>77</v>
@@ -19999,10 +20002,10 @@
         <v>150</v>
       </c>
       <c r="Y168" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="Z168" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>77</v>
@@ -20020,7 +20023,7 @@
         <v>77</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>75</v>
@@ -20037,10 +20040,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -20063,19 +20066,19 @@
         <v>77</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>77</v>
@@ -20124,7 +20127,7 @@
         <v>77</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>75</v>
@@ -20136,15 +20139,15 @@
         <v>91</v>
       </c>
       <c r="AJ169" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -20170,10 +20173,10 @@
         <v>99</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="N170" t="s" s="2">
         <v>328</v>
@@ -20226,7 +20229,7 @@
         <v>77</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>75</v>
@@ -20243,10 +20246,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -20269,16 +20272,16 @@
         <v>85</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
@@ -20328,7 +20331,7 @@
         <v>77</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>75</v>
@@ -20345,10 +20348,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -20371,16 +20374,16 @@
         <v>85</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
@@ -20430,7 +20433,7 @@
         <v>77</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>75</v>
@@ -20447,10 +20450,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -20473,19 +20476,19 @@
         <v>85</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="O173" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>77</v>
@@ -20534,7 +20537,7 @@
         <v>77</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>75</v>
@@ -20551,10 +20554,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -20651,10 +20654,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -20753,14 +20756,14 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
@@ -20782,10 +20785,10 @@
         <v>105</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="N176" t="s" s="2">
         <v>108</v>
@@ -20840,7 +20843,7 @@
         <v>77</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>75</v>
@@ -20857,10 +20860,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -20886,13 +20889,13 @@
         <v>283</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="O177" t="s" s="2">
         <v>426</v>
@@ -20923,10 +20926,10 @@
         <v>150</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>77</v>
@@ -20944,7 +20947,7 @@
         <v>77</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>84</v>
@@ -20961,10 +20964,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -20987,16 +20990,16 @@
         <v>85</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="M178" t="s" s="2">
         <v>531</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="O178" t="s" s="2">
         <v>524</v>
@@ -21048,7 +21051,7 @@
         <v>77</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>75</v>
@@ -21065,10 +21068,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -21094,16 +21097,16 @@
         <v>283</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>77</v>
@@ -21131,10 +21134,10 @@
         <v>142</v>
       </c>
       <c r="Y179" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="Z179" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>77</v>
@@ -21152,7 +21155,7 @@
         <v>77</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>75</v>
@@ -21161,7 +21164,7 @@
         <v>84</v>
       </c>
       <c r="AI179" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AJ179" t="s" s="2">
         <v>92</v>
@@ -21169,14 +21172,14 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E180" s="2"/>
       <c r="F180" t="s" s="2">
@@ -21198,16 +21201,16 @@
         <v>283</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="O180" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>77</v>
@@ -21235,10 +21238,10 @@
         <v>142</v>
       </c>
       <c r="Y180" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="Z180" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>77</v>
@@ -21256,7 +21259,7 @@
         <v>77</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>75</v>
@@ -21273,10 +21276,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -21302,16 +21305,16 @@
         <v>78</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="O181" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>77</v>
@@ -21360,7 +21363,7 @@
         <v>77</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>75</v>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T05:48:26+00:00</t>
+    <t>2026-09-03T10:47:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T10:47:18+00:00</t>
+    <t>2026-09-08T14:02:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-alpha.6</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T14:02:02+00:00</t>
+    <t>2026-09-09T10:10:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T10:10:08+00:00</t>
+    <t>2026-09-09T13:56:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T13:56:56+00:00</t>
+    <t>2026-09-09T14:11:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:11:38+00:00</t>
+    <t>2026-09-09T14:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:19:13+00:00</t>
+    <t>2026-09-09T14:42:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:42:29+00:00</t>
+    <t>2026-09-09T15:55:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T15:55:32+00:00</t>
+    <t>2026-09-10T12:50:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1349,7 +1349,7 @@
 </t>
   </si>
   <si>
-    <t>Es werden bevorzugt LOINC-Codes ohne präkoordinierte Specimentype-Angabe verwendet (System = XXX); der Specimentype wird separat über Specimen.type kodiert.</t>
+    <t>Es werden bevorzugt LOINC-Codes ohne präkoordinierte Specimentype-Angabe verwendet (System = XXX); der Specimentype wird separat über Specimen.type kodiert. AUSNAHME fuer die serologische Anwendung dieses Profils — qualitativer Antigen- oder Antikoerpernachweis: Dort ist ein praekoordiniertes Specimen zulaessig, weil in der Serologie nur wenige Materialien vorkommen, ueberwiegend Serum.</t>
   </si>
   <si>
     <t>LOINC-Code, der den gemessenen Laborparameter bzw. durchgeführten Labortest beschreibt.</t>
@@ -2124,7 +2124,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-probe)
 </t>
   </si>
   <si>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T12:50:06+00:00</t>
+    <t>2026-09-10T13:10:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:10:47+00:00</t>
+    <t>2026-09-10T13:32:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:32:54+00:00</t>
+    <t>2026-09-10T13:47:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:47:44+00:00</t>
+    <t>2026-09-10T16:40:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:40:19+00:00</t>
+    <t>2026-09-10T17:22:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:22:53+00:00</t>
+    <t>2026-09-10T17:39:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:39:40+00:00</t>
+    <t>2026-09-10T18:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T18:06:33+00:00</t>
+    <t>2026-09-11T06:33:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T06:33:50+00:00</t>
+    <t>2026-09-11T11:07:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T11:07:28+00:00</t>
+    <t>2026-09-11T11:48:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T11:48:22+00:00</t>
+    <t>2026-09-11T12:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:41:50+00:00</t>
+    <t>2026-09-11T12:56:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:56:10+00:00</t>
+    <t>2026-09-12T16:17:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,13 +87,13 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Spezifische Bestimmung beschreibt den qualitativen Nachweis eines vordefinierten mikrobiellen Ziels in einer Probe durch direkte molekulare, immunologische oder biochemische Nachweismethoden sowie durch methodenneutral kodierte Nachweistests. Der kulturbasierte zielgerichtete Nachweis wird über MII_PR_Mikrobio_Spezifische_Kultur abgebildet.</t>
+    <t>Spezifische Bestimmung beschreibt den qualitativen Nachweis eines vordefinierten mikrobiellen Ziels in einer Probe durch direkte molekulare, immunologische oder biochemische Nachweismethoden sowie durch methodenneutral kodierte Nachweistests. Der kulturbasierte zielgerichtete Nachweis liegt ebenfalls hier; das Verfahren steht im Untersuchungscode und in Observation.method.</t>
   </si>
   <si>
     <t>Purpose</t>
   </si>
   <si>
-    <t>Dieses Profil beschreibt den zielgerichteten, nicht kulturbasierten Nachweis. Es bildet auch das negative Ergebnis eines zielgerichteten Erregernachweises ab, z. B. einen negativen VRE-Nachweis über 105904-7 mit dem Wert 'Not detected'.</t>
+    <t>Dieses Profil beschreibt den zielgerichteten Nachweis, unabhaengig davon, ob er molekular, immunologisch, biochemisch oder kulturell erfolgt. Es bildet auch das negative Ergebnis eines zielgerichteten Erregernachweises ab, z. B. einen negativen VRE-Nachweis über 105904-7 mit dem Wert 'Not detected'.</t>
   </si>
   <si>
     <t>Copyright</t>
@@ -1688,7 +1688,7 @@
     <t>valueCodeableConcept</t>
   </si>
   <si>
-    <t>Nachweis oder Ausschluss des im Code benannten Ziels. Ein grenzwertiger Befund wird als 'Weakly positive' oder 'Equivocal result' berichtet — das ist eine Aussage und gehört deshalb hierher. Ein unbestimmbares Ergebnis, bei dem die Untersuchung gar keine verwertbare Aussage liefert (z. B. inhibierte PCR), wird dagegen über dataAbsentReason abgebildet.</t>
+    <t>Nachweis oder Ausschluss des im Code benannten Ziels — auch dann, wenn er kulturell erfolgte: Eine zielgerichtete Kultur berichtet 'Detected' oder 'Not detected' und nicht 'Organism growth', weil die Kultur schon im Untersuchungscode steht (Ballotfrage 7). Ein grenzwertiger Befund wird als 'Weakly positive' oder 'Equivocal result' berichtet — das ist eine Aussage und gehört deshalb hierher. Ein unbestimmbares Ergebnis, bei dem die Untersuchung gar keine verwertbare Aussage liefert (z. B. inhibierte PCR), wird dagegen über dataAbsentReason abgebildet.</t>
   </si>
   <si>
     <t>The information determined as a result of making the observation, if the information has a simple value.</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T16:17:49+00:00</t>
+    <t>2026-09-12T17:15:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-spezifische-bestimmung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T17:15:10+00:00</t>
+    <t>2026-09-12T20:14:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
